--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2630-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2630-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B70D881B-A346-43DA-8182-780348068255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{52DA7B86-0CA0-472D-A373-F7CCC2F82F53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{2D6A22D0-6F03-4057-ACD7-2F631B67CFE5}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{E361813A-CCE4-4EB6-9FC8-3F8260AAE0E3}"/>
   </bookViews>
   <sheets>
     <sheet name="2630-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1520,25 +1520,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D02C2D0-2CFC-49B9-B90D-EAAD417794FE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21627B7F-E978-4567-989C-2AA85C5ED368}">
   <dimension ref="A1:X25"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1572,7 +1571,7 @@
       <c r="W1" s="31"/>
       <c r="X1" s="23"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1608,7 +1607,7 @@
       <c r="W2" s="33"/>
       <c r="X2" s="34"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1660,7 +1659,7 @@
       </c>
       <c r="X3" s="37"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1728,7 +1727,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>2024</v>
       </c>
@@ -1800,7 +1799,7 @@
         <v>2.11</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="40">
         <v>2023</v>
       </c>
@@ -1872,7 +1871,7 @@
         <v>1.82</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>2022</v>
       </c>
@@ -1944,7 +1943,7 @@
         <v>2.1800000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="42">
         <v>2021</v>
       </c>
@@ -2016,7 +2015,7 @@
         <v>6.36</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="44"/>
       <c r="B9" s="45"/>
       <c r="C9" s="18" t="s">
@@ -2044,7 +2043,7 @@
       <c r="W9" s="51"/>
       <c r="X9" s="47"/>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="52">
         <v>2020</v>
       </c>
@@ -2116,7 +2115,7 @@
         <v>3.74</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="54"/>
       <c r="B11" s="55"/>
       <c r="C11" s="20" t="s">
@@ -2144,7 +2143,7 @@
       <c r="W11" s="61"/>
       <c r="X11" s="57"/>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="42">
         <v>2019</v>
       </c>
@@ -2216,7 +2215,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="44"/>
       <c r="B13" s="45"/>
       <c r="C13" s="18" t="s">
@@ -2244,7 +2243,7 @@
       <c r="W13" s="51"/>
       <c r="X13" s="47"/>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="38">
         <v>2018</v>
       </c>
@@ -2316,7 +2315,7 @@
         <v>5.62</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="40">
         <v>2017</v>
       </c>
@@ -2388,7 +2387,7 @@
         <v>3.56</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="38">
         <v>2016</v>
       </c>
@@ -2460,7 +2459,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="40">
         <v>2015</v>
       </c>
@@ -2532,7 +2531,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="38">
         <v>2014</v>
       </c>
@@ -2604,7 +2603,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="40">
         <v>2013</v>
       </c>
@@ -2676,7 +2675,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="38">
         <v>2012</v>
       </c>
@@ -2748,7 +2747,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="40">
         <v>2011</v>
       </c>
@@ -2820,7 +2819,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="38">
         <v>2010</v>
       </c>
@@ -2892,7 +2891,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="40">
         <v>2009</v>
       </c>
@@ -2964,7 +2963,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="38">
         <v>2008</v>
       </c>
@@ -3036,7 +3035,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="40" t="s">
         <v>41</v>
       </c>
